--- a/SELECT_ITEM_追加用スプレッドシート.xlsx
+++ b/SELECT_ITEM_追加用スプレッドシート.xlsx
@@ -9314,7 +9314,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>T1000 真っ白</t>
+          <t>T1000 ホワイト色</t>
         </is>
       </c>
       <c r="E126" s="133" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>T1702 黄みがかった白</t>
+          <t>T1702 ウォームホワイト色</t>
         </is>
       </c>
       <c r="E127" s="134" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>T1020 赤みがかった白</t>
+          <t>T1020 レッドクリーム色</t>
         </is>
       </c>
       <c r="E128" s="135" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>T1030 オレンジがかった白</t>
+          <t>T1030 イエロークリーム色</t>
         </is>
       </c>
       <c r="E129" s="136" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>T3001</t>
+          <t>T3001 ライトグレー色</t>
         </is>
       </c>
       <c r="E130" s="137" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>T5001</t>
+          <t>T5001 グレー色</t>
         </is>
       </c>
       <c r="E131" s="138" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>T6013</t>
+          <t>T6013 ダークグレー色</t>
         </is>
       </c>
       <c r="E132" s="139" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>JP-100BK</t>
+          <t>JP-100BK ブラック色</t>
         </is>
       </c>
       <c r="E133" s="140" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>T6010</t>
+          <t>T6010 ライトブラウン色</t>
         </is>
       </c>
       <c r="E134" s="141" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>T6404</t>
+          <t>T6404 ダークブラウン色</t>
         </is>
       </c>
       <c r="E135" s="142" t="inlineStr">
@@ -13371,8 +13371,16 @@
         <f>'商品マスタ'!E27</f>
         <v/>
       </c>
-      <c r="C27" s="8" t="inlineStr"/>
-      <c r="D27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>おすすめカラーはこちら</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>jolipate_color.html</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="8" t="inlineStr"/>
     </row>
@@ -14992,10 +15000,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C2:C110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"カタログを見る【関東】,カタログを見る【九州】,カタログを見る,Wikipediaを見る"</formula1>
+      <formula1>"カタログを見る【関東】,カタログを見る【九州】,カタログを見る,おすすめカラーはこちら,Wikipediaを見る"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"カタログを見る【関東】,カタログを見る【九州】,カタログを見る,Wikipediaを見る"</formula1>
+      <formula1>"カタログを見る【関東】,カタログを見る【九州】,カタログを見る,おすすめカラーはこちら,Wikipediaを見る"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
